--- a/data/horarios-141-2026-09-28.xlsx
+++ b/data/horarios-141-2026-09-28.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:57:47</t>
+          <t>Última actualización: 18:31:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 26</t>
+          <t>Total filas: 49</t>
         </is>
       </c>
     </row>
@@ -1159,6 +1159,604 @@
         </is>
       </c>
       <c r="F31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>18:32</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>2</v>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>18:34</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>4</v>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>18:36</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>6</v>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>18:40</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>26_155 Y 38-B MALVINAS</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>10</v>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>12</v>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>16</v>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>30</v>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>19:02</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>32</v>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>19:05</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>35</v>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>16_P MOR-SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>40</v>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>48</v>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>48</v>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>19:20</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>16_SANTA ANA</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>50</v>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>19:21</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>51</v>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr"/>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>19:28</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>58</v>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>19:30</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>17_ROMERO</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>60</v>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>19:39</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>69</v>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>15_ABASTO</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>76</v>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>19:46</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>76</v>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>19:53</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>83</v>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>95</v>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>20:05</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>27_EL RETIRO</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>95</v>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>20:06</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>16_P MOR-167 Y 521</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>96</v>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1171,7 +1769,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1184,14 +1782,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:57:47</t>
+          <t>Última actualización: 18:31:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 1</t>
+          <t>Total filas: 4</t>
         </is>
       </c>
     </row>
@@ -1252,6 +1850,84 @@
         </is>
       </c>
       <c r="F6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>12</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>18:46</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>215B_EL PATO</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>18:30:50</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>19:18</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>215C_EL PATO</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>48</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1264,7 +1940,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1277,14 +1953,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 12:57:47</t>
+          <t>Última actualización: 18:31:31</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 6</t>
+          <t>Total filas: 9</t>
         </is>
       </c>
     </row>
@@ -1475,6 +2151,84 @@
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>18:31:11</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18:42</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>215C_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>L6203</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>18:31:31</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18:50</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>215B_LP-P MOR-1 Y 57</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>19</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>18:31:31</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>18:55</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>24</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/horarios-141-2026-09-28.xlsx
+++ b/data/horarios-141-2026-09-28.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F54"/>
+  <dimension ref="A1:F64"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,14 +441,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:31:31</t>
+          <t>Última actualización: 22:16:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 49</t>
+          <t>Total filas: 59</t>
         </is>
       </c>
     </row>
@@ -1757,6 +1757,266 @@
         </is>
       </c>
       <c r="F54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>22:15:26</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>22:20</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>5</v>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>22:15:26</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>22:21</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>26_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>6</v>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>22:15:26</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>22:23</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>10_OLMOS</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>8</v>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>22:15:26</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>22:32</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>84_COLONIA URQUIZA-ESC 49</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>17</v>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>22:15:26</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>22:54</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>14_ABASTO</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>39</v>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>22:15:26</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>23:08</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>14X44_ABASTO</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>53</v>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>22:15:26</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>23:14</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>23_HERNANDEZ</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>59</v>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>22:15:26</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>23:23</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>11_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>68</v>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>22:15:26</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>23:38</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>215_ALUAR</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>83</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>22:15:26</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>23:53</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>11X44_ETCHEVERRY</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>98</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1769,7 +2029,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1782,14 +2042,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:31:31</t>
+          <t>Última actualización: 22:16:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 4</t>
+          <t>Total filas: 5</t>
         </is>
       </c>
     </row>
@@ -1928,6 +2188,32 @@
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>22:15:26</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>23:38</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>215_ALUAR</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>83</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>LP1912</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1940,7 +2226,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1953,14 +2239,14 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>Última actualización: 18:31:31</t>
+          <t>Última actualización: 22:16:12</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>Total filas: 9</t>
+          <t>Total filas: 10</t>
         </is>
       </c>
     </row>
@@ -2229,6 +2515,32 @@
         </is>
       </c>
       <c r="F14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>22:16:12</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>22:22</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>215A_LA PLATA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>6</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>L6173</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
